--- a/excel/Max-Flow-Capacities.xlsx
+++ b/excel/Max-Flow-Capacities.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -599,7 +599,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
